--- a/artfynd/A 41169-2022 artfynd.xlsx
+++ b/artfynd/A 41169-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41169-2022 artfynd.xlsx
+++ b/artfynd/A 41169-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107978553</v>
+        <v>107978555</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fransmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603380.2548833229</v>
+        <v>603370</v>
       </c>
       <c r="R2" t="n">
-        <v>7044384.400745686</v>
+        <v>7044380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,55 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107978556</v>
+        <v>107978551</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fransmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603355.4221052299</v>
+        <v>603423</v>
       </c>
       <c r="R3" t="n">
-        <v>7044363.938851732</v>
+        <v>7044417</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +840,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107978551</v>
+        <v>107978552</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603422.5841462146</v>
+        <v>603353</v>
       </c>
       <c r="R4" t="n">
-        <v>7044417.04562557</v>
+        <v>7044381</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +937,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107978552</v>
+        <v>107978554</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603353.084225142</v>
+        <v>603380</v>
       </c>
       <c r="R5" t="n">
-        <v>7044380.838285353</v>
+        <v>7044384</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1034,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,50 +1063,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107978555</v>
+        <v>107978553</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fransmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603370.1078365438</v>
+        <v>603380</v>
       </c>
       <c r="R6" t="n">
-        <v>7044380.050811097</v>
+        <v>7044384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1136,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107978554</v>
+        <v>107978556</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,34 +1176,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fransmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603380.2548833229</v>
+        <v>603356</v>
       </c>
       <c r="R7" t="n">
-        <v>7044384.400745686</v>
+        <v>7044364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,19 +1238,9 @@
           <t>2023-04-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 41169-2022 artfynd.xlsx
+++ b/artfynd/A 41169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978551</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978554</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,8 +1294,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107978556</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>